--- a/TestData/OpenCard_LoginData.xlsx
+++ b/TestData/OpenCard_LoginData.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A822358\Downloads\Eclipse_Workspace\OpenCartV121\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8131F6E4-9CDB-4585-92E9-2224F39C2D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3748BAB2-60B9-4E5B-9816-FBEF50332B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>Email</t>
   </si>
@@ -64,12 +65,28 @@
   </si>
   <si>
     <t>invalid</t>
+  </si>
+  <si>
+    <t>emailid</t>
+  </si>
+  <si>
+    <t>anflo@gmail.com</t>
+  </si>
+  <si>
+    <t>23242@hotmail.com</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>Valid Email</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -87,12 +104,22 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -108,9 +135,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -395,18 +424,18 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.36328125" customWidth="1"/>
-    <col min="2" max="2" width="23.90625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="22.36328125"/>
+    <col min="2" max="2" customWidth="true" width="23.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>5</v>
       </c>
     </row>
@@ -417,7 +446,7 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>4</v>
       </c>
     </row>
@@ -428,7 +457,7 @@
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>10</v>
       </c>
     </row>
@@ -436,10 +465,10 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>10</v>
       </c>
     </row>
@@ -450,7 +479,7 @@
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>11</v>
       </c>
     </row>
@@ -458,26 +487,26 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B7">
+      <c r="B7" s="0">
         <v>323553535</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>0</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>0</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>12</v>
       </c>
     </row>
@@ -494,4 +523,48 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BDFDD7-154E-4149-ACAE-CDACA096B1F1}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="19.81640625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{40C70C17-9915-4A5A-8A3C-CF96DE812164}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{B3049C4E-3298-4BE0-B3F6-F128457DD824}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{62E7956E-30C5-45B0-A3B1-BEC76487B295}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>